--- a/assets/constructions/examples/ctd_mie_mfunc.xlsx
+++ b/assets/constructions/examples/ctd_mie_mfunc.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -654,11 +654,31 @@
           <t>zefp</t>
         </is>
       </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CGMC5/8C22-65-11-3</t>
+          <t>GMC20W17-30-9-3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -668,7 +688,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TMSD Vertical - Indexable Vertical Inserts</t>
+          <t>MegaLiner</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -681,14 +701,22 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>BOTH</t>
+          <t>INTERNAL</t>
         </is>
       </c>
       <c r="M2" t="n">
         <v>3</v>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>VAR_GMC_09</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>VARGUS</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
         <v>0</v>
@@ -697,22 +725,24 @@
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="T2" t="inlineStr"/>
+        <v>16.7</v>
+      </c>
+      <c r="T2" t="n">
+        <v>16.7</v>
+      </c>
       <c r="U2" t="n">
-        <v>15.88</v>
+        <v>20</v>
       </c>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="X2" t="n">
-        <v>64.999</v>
+        <v>30</v>
       </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="n">
-        <v>135.001</v>
+        <v>105</v>
       </c>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
@@ -733,39 +763,53 @@
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>HA</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>HA-15.875</t>
+          <t>HB-20</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>VARGUS_V:11V</t>
+          <t>VARGUS_9VN</t>
         </is>
       </c>
       <c r="AP2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
         <v>0</v>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>2018/VARGUS2018-ENGweb,pdf</t>
+          <t>2018/VARGUS Catalog VARDEX</t>
         </is>
       </c>
       <c r="AS2" t="n">
         <v>1</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>193.5</v>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AW2" t="n">
+        <v>17789.17</v>
       </c>
     </row>
     <row r="3">
@@ -890,11 +934,25 @@
       <c r="AS3" t="n">
         <v>1</v>
       </c>
+      <c r="AT3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>402.85</v>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AW3" t="n">
+        <v>37035.49</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CGMC9C13-45-7-3</t>
+          <t>GMC100W085-175-11-3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -904,7 +962,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MegaLiner</t>
+          <t>TMSD Vertical - Indexable Vertical Inserts</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -917,22 +975,14 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>INTERNAL</t>
+          <t>BOTH</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>3</v>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>VAR_CGMC_07</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>VARGUS</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
         <v>0</v>
@@ -941,24 +991,22 @@
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="T4" t="n">
-        <v>12.7</v>
-      </c>
+        <v>22.7</v>
+      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
-        <v>9</v>
+        <v>25.4</v>
       </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="X4" t="n">
-        <v>45</v>
+        <v>44.45</v>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>115</v>
+        <v>113.995</v>
       </c>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
@@ -969,7 +1017,7 @@
         <v>1</v>
       </c>
       <c r="AG4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -979,45 +1027,59 @@
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>HA</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>R</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>HA-9</t>
+          <t>HB-25.4</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>VARGUS_7VN</t>
+          <t>VARGUS_V:11V</t>
         </is>
       </c>
       <c r="AP4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ4" t="n">
         <v>0</v>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>2018/VARGUS Catalog VARDEX</t>
+          <t>2018/VARGUS2018-ENGweb,pdf</t>
         </is>
       </c>
       <c r="AS4" t="n">
         <v>1</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>214.6</v>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AW4" t="n">
+        <v>19728.97</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GMC075W066-118-9-3</t>
+          <t>GMC25W22-45-11-3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1027,7 +1089,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TMSD Vertical - Indexable Vertical Inserts</t>
+          <t>MegaLiner</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -1040,7 +1102,7 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>BOTH</t>
+          <t>INTERNAL</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -1048,10 +1110,14 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>VARGUS_V:9V</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
+          <t>VAR_GMC_11</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>VARGUS</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1060,22 +1126,24 @@
         <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="T5" t="inlineStr"/>
+        <v>20.8</v>
+      </c>
+      <c r="T5" t="n">
+        <v>20.8</v>
+      </c>
       <c r="U5" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="X5" t="n">
-        <v>29.845</v>
+        <v>45</v>
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>102.006</v>
+        <v>115</v>
       </c>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
@@ -1101,50 +1169,64 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>N</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>HB-19</t>
+          <t>HB-25</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>VARGUS_V:9V</t>
+          <t>VARGUS_11VN</t>
         </is>
       </c>
       <c r="AP5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
         <v>0</v>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>2018/VARGUS2018-ENGweb,pdf</t>
+          <t>2018/VARGUS Catalog VARDEX</t>
         </is>
       </c>
       <c r="AS5" t="n">
         <v>1</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>214.6</v>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AW5" t="n">
+        <v>19728.97</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CGMC15C22-65-11-3</t>
+          <t>327-16B24SC-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VARGUS</t>
+          <t>SANDVIK</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MegaLiner</t>
+          <t xml:space="preserve">CoroMill® 327 </t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -1165,12 +1247,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>VAR_CGMC_11</t>
+          <t>CoroMill 327 -size 12</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>VARGUS</t>
+          <t>SANDVIK</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -1181,29 +1263,35 @@
         <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>20.8</v>
+        <v>21.7</v>
       </c>
       <c r="T6" t="n">
-        <v>20.8</v>
+        <v>21.7</v>
       </c>
       <c r="U6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="X6" t="n">
-        <v>65</v>
+        <v>18.3</v>
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="n">
-        <v>135</v>
+        <v>74.3</v>
       </c>
       <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
+      <c r="AB6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>5.15</v>
+      </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="n">
         <v>1</v>
@@ -1219,7 +1307,7 @@
       <c r="AI6" t="inlineStr"/>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>HA</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1227,32 +1315,40 @@
           <t>N</t>
         </is>
       </c>
-      <c r="AL6" t="inlineStr"/>
+      <c r="AL6" t="n">
+        <v>40000</v>
+      </c>
       <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>HA-15</t>
+          <t>HB-16</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>VARGUS_11VN</t>
+          <t>COR_327:12</t>
         </is>
       </c>
       <c r="AP6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ6" t="n">
         <v>0</v>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>2018/VARGUS Catalog VARDEX</t>
+          <t>2020 / Coromant WebSite</t>
         </is>
       </c>
       <c r="AS6" t="n">
         <v>1</v>
       </c>
+      <c r="AT6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
